--- a/assets/constructions/examples/ctd_mie_threadmill.xlsx
+++ b/assets/constructions/examples/ctd_mie_threadmill.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,11 +644,31 @@
           <t>zefp</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CTM1SC1/2"C21-75-3L</t>
+          <t>RTMC3236-65B4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -658,7 +678,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CTM SC</t>
+          <t>RTMC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -674,7 +694,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
@@ -683,7 +703,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -692,7 +712,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>VAR_TM_3/8L</t>
+          <t>VAR_*RT_41</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -702,28 +722,30 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>21.6</v>
+        <v>35.9</v>
       </c>
       <c r="W2" t="n">
-        <v>12.7</v>
+        <v>32</v>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>28.3</v>
+      </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
@@ -733,7 +755,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -741,7 +763,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -753,12 +775,12 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>HA-12.7</t>
+          <t>HB-32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>VARGUS_41N</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -773,13 +795,27 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>34224.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TMC25-5CW</t>
+          <t>BTMLC25-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -789,7 +825,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TMC</t>
+          <t>BTMLC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -823,7 +859,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>VAR_TM_5/8</t>
+          <t>VAR_TM_3/8</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,24 +875,24 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
         <v>25</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>18.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>52</v>
+        <v>63.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
@@ -891,7 +927,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>VARGUS_3/8T_TMC</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -907,12 +943,26 @@
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>31769.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RTMC2522-43L3</t>
+          <t>RTMC2522-55S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -956,7 +1006,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>VAR_*RT_40</t>
+          <t>VAR_*RT_25</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -982,10 +1032,10 @@
         <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
@@ -1024,7 +1074,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>VARGUS_40N</t>
+          <t>VARGUS_25N</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1040,12 +1090,26 @@
       </c>
       <c r="AQ4" t="n">
         <v>3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>29756.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RTMOC25C30-90B4</t>
+          <t>TMMC12-6.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1055,7 +1119,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MiTM</t>
+          <t>TMMC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1071,7 +1135,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
@@ -1080,14 +1144,18 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>VAR_TM_6</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>VARGUS</t>
@@ -1095,29 +1163,31 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>30.5</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>57</v>
+      </c>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
@@ -1134,24 +1204,24 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HB-12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>VARGUS_41N</t>
+          <t>VARGUS_TMMC1220-6.0</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1162,17 +1232,31 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2022 / Full MAIN VARDEX 2022-METRIC.pdf</t>
+          <t>2018/VARGUS2018-ENGweb,pdf</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>204.55</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>17976.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTM2SC14C21-65-2U</t>
+          <t>TMC25-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1182,7 +1266,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CTM SC</t>
+          <t>TMC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1198,7 +1282,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
@@ -1207,7 +1291,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1216,7 +1300,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>VAR_TM_1/4U</t>
+          <t>VAR_TM_5/8</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1226,28 +1310,30 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>20.65</v>
+        <v>30</v>
       </c>
       <c r="W6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>24</v>
+      </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="AA6" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
@@ -1257,7 +1343,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1265,7 +1351,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1277,12 +1363,12 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>VARGUS_1/4UEI_TMC</t>
+          <t>VARGUS_TMC25-5-124/008</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1297,7 +1383,21 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>267.96</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>23549.02</v>
       </c>
     </row>
   </sheetData>
